--- a/src/job_crawler/assets/job-template.xlsx
+++ b/src/job_crawler/assets/job-template.xlsx
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>选填。保留源站截止日期或 ISO 日期时间，以文本填写；未提供时留空。只有日期时不补造具体时刻。</t>
+          <t>选填。统一为 YYYY-MM-DD 文本，例如 1970-01-01；无截止日期时留空。精确时间按北京时间取日期；原始时间保留在采集 JSON 中。</t>
         </is>
       </c>
     </row>
